--- a/data/qPCR/qPCR-sample-code.xlsx
+++ b/data/qPCR/qPCR-sample-code.xlsx
@@ -5,17 +5,17 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/af327/Library/CloudStorage/Box-Box/TEAM 01: Gunsch_ Research_Group/Amelia Foley/Research/Results/Aim 2/qPCR/Sampling/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/af327/Desktop/R/encapsulation/data/qPCR/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73FE8D4E-3F09-9542-8125-26ACA2623F51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71802C12-A6D0-D74F-BC2F-90B90089CE7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="520" yWindow="760" windowWidth="27240" windowHeight="17280" xr2:uid="{EDF4EF0B-C212-D947-900A-D35861327F1A}"/>
+    <workbookView xWindow="520" yWindow="760" windowWidth="27240" windowHeight="17780" xr2:uid="{EDF4EF0B-C212-D947-900A-D35861327F1A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="181029" iterateCount="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="287" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="692" uniqueCount="156">
   <si>
     <t>day</t>
   </si>
@@ -261,6 +261,249 @@
   </si>
   <si>
     <t>K-CAC-0</t>
+  </si>
+  <si>
+    <t>R-FA-14</t>
+  </si>
+  <si>
+    <t>R-FB-14</t>
+  </si>
+  <si>
+    <t>R-FC-14</t>
+  </si>
+  <si>
+    <t>R-CA-14</t>
+  </si>
+  <si>
+    <t>R-CB-14</t>
+  </si>
+  <si>
+    <t>R-CC-14</t>
+  </si>
+  <si>
+    <t>R-CAC-14</t>
+  </si>
+  <si>
+    <t>R-CBC-14</t>
+  </si>
+  <si>
+    <t>R-CCC-14</t>
+  </si>
+  <si>
+    <t>K-FA-14</t>
+  </si>
+  <si>
+    <t>K-FB-14</t>
+  </si>
+  <si>
+    <t>K-FC-14</t>
+  </si>
+  <si>
+    <t>K-CA-14</t>
+  </si>
+  <si>
+    <t>K-CB-14</t>
+  </si>
+  <si>
+    <t>K-CC-14</t>
+  </si>
+  <si>
+    <t>K-CAC-14</t>
+  </si>
+  <si>
+    <t>K-CBC-14</t>
+  </si>
+  <si>
+    <t>K-CCC-14</t>
+  </si>
+  <si>
+    <t>M-FA-14</t>
+  </si>
+  <si>
+    <t>M-FB-14</t>
+  </si>
+  <si>
+    <t>M-FC-14</t>
+  </si>
+  <si>
+    <t>M-CA-14</t>
+  </si>
+  <si>
+    <t>M-CB-14</t>
+  </si>
+  <si>
+    <t>M-CC-14</t>
+  </si>
+  <si>
+    <t>M-CAC-14</t>
+  </si>
+  <si>
+    <t>M-CBC-14</t>
+  </si>
+  <si>
+    <t>M-CCC-14</t>
+  </si>
+  <si>
+    <t>R-FA-21</t>
+  </si>
+  <si>
+    <t>R-FB-21</t>
+  </si>
+  <si>
+    <t>R-FC-21</t>
+  </si>
+  <si>
+    <t>R-CA-21</t>
+  </si>
+  <si>
+    <t>R-CB-21</t>
+  </si>
+  <si>
+    <t>R-CC-21</t>
+  </si>
+  <si>
+    <t>R-CAC-21</t>
+  </si>
+  <si>
+    <t>R-CBC-21</t>
+  </si>
+  <si>
+    <t>R-CCC-21</t>
+  </si>
+  <si>
+    <t>K-FA-21</t>
+  </si>
+  <si>
+    <t>K-FB-21</t>
+  </si>
+  <si>
+    <t>K-FC-21</t>
+  </si>
+  <si>
+    <t>K-CA-21</t>
+  </si>
+  <si>
+    <t>K-CB-21</t>
+  </si>
+  <si>
+    <t>K-CC-21</t>
+  </si>
+  <si>
+    <t>K-CAC-21</t>
+  </si>
+  <si>
+    <t>K-CBC-21</t>
+  </si>
+  <si>
+    <t>K-CCC-21</t>
+  </si>
+  <si>
+    <t>M-FA-21</t>
+  </si>
+  <si>
+    <t>M-FB-21</t>
+  </si>
+  <si>
+    <t>M-FC-21</t>
+  </si>
+  <si>
+    <t>M-CA-21</t>
+  </si>
+  <si>
+    <t>M-CB-21</t>
+  </si>
+  <si>
+    <t>M-CC-21</t>
+  </si>
+  <si>
+    <t>M-CAC-21</t>
+  </si>
+  <si>
+    <t>M-CBC-21</t>
+  </si>
+  <si>
+    <t>M-CCC-21</t>
+  </si>
+  <si>
+    <t>R-FA-42</t>
+  </si>
+  <si>
+    <t>R-FB-42</t>
+  </si>
+  <si>
+    <t>R-FC-42</t>
+  </si>
+  <si>
+    <t>R-CA-42</t>
+  </si>
+  <si>
+    <t>R-CB-42</t>
+  </si>
+  <si>
+    <t>R-CC-42</t>
+  </si>
+  <si>
+    <t>R-CAC-42</t>
+  </si>
+  <si>
+    <t>R-CBC-42</t>
+  </si>
+  <si>
+    <t>R-CCC-42</t>
+  </si>
+  <si>
+    <t>K-FA-42</t>
+  </si>
+  <si>
+    <t>K-FB-42</t>
+  </si>
+  <si>
+    <t>K-FC-42</t>
+  </si>
+  <si>
+    <t>K-CA-42</t>
+  </si>
+  <si>
+    <t>K-CB-42</t>
+  </si>
+  <si>
+    <t>K-CC-42</t>
+  </si>
+  <si>
+    <t>K-CAC-42</t>
+  </si>
+  <si>
+    <t>K-CBC-42</t>
+  </si>
+  <si>
+    <t>K-CCC-42</t>
+  </si>
+  <si>
+    <t>M-FA-42</t>
+  </si>
+  <si>
+    <t>M-FB-42</t>
+  </si>
+  <si>
+    <t>M-FC-42</t>
+  </si>
+  <si>
+    <t>M-CA-42</t>
+  </si>
+  <si>
+    <t>M-CB-42</t>
+  </si>
+  <si>
+    <t>M-CC-42</t>
+  </si>
+  <si>
+    <t>M-CAC-42</t>
+  </si>
+  <si>
+    <t>M-CBC-42</t>
+  </si>
+  <si>
+    <t>M-CCC-42</t>
   </si>
 </sst>
 </file>
@@ -296,9 +539,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -633,7 +875,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C57FC14D-4CDD-7743-924D-FD4816D37885}">
-  <dimension ref="A1:I55"/>
+  <dimension ref="A1:I136"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="4" max="4" width="12.1640625" bestFit="1" customWidth="1"/>
@@ -985,7 +1227,7 @@
       <c r="H12">
         <v>50</v>
       </c>
-      <c r="I12" s="1">
+      <c r="I12">
         <v>1.74</v>
       </c>
     </row>
@@ -2234,6 +2476,2112 @@
       </c>
       <c r="I55">
         <v>2.68</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A56" t="s">
+        <v>75</v>
+      </c>
+      <c r="B56" t="s">
+        <v>5</v>
+      </c>
+      <c r="C56" t="s">
+        <v>3</v>
+      </c>
+      <c r="D56" t="s">
+        <v>4</v>
+      </c>
+      <c r="E56" t="s">
+        <v>15</v>
+      </c>
+      <c r="F56">
+        <v>14</v>
+      </c>
+      <c r="G56">
+        <v>1</v>
+      </c>
+      <c r="H56">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A57" t="s">
+        <v>76</v>
+      </c>
+      <c r="B57" t="s">
+        <v>6</v>
+      </c>
+      <c r="C57" t="s">
+        <v>3</v>
+      </c>
+      <c r="D57" t="s">
+        <v>4</v>
+      </c>
+      <c r="E57" t="s">
+        <v>15</v>
+      </c>
+      <c r="F57">
+        <v>14</v>
+      </c>
+      <c r="G57">
+        <v>1</v>
+      </c>
+      <c r="H57">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A58" t="s">
+        <v>77</v>
+      </c>
+      <c r="B58" t="s">
+        <v>7</v>
+      </c>
+      <c r="C58" t="s">
+        <v>3</v>
+      </c>
+      <c r="D58" t="s">
+        <v>4</v>
+      </c>
+      <c r="E58" t="s">
+        <v>15</v>
+      </c>
+      <c r="F58">
+        <v>14</v>
+      </c>
+      <c r="G58">
+        <v>1</v>
+      </c>
+      <c r="H58">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A59" t="s">
+        <v>78</v>
+      </c>
+      <c r="B59" t="s">
+        <v>5</v>
+      </c>
+      <c r="C59" t="s">
+        <v>3</v>
+      </c>
+      <c r="D59" t="s">
+        <v>17</v>
+      </c>
+      <c r="E59" t="s">
+        <v>16</v>
+      </c>
+      <c r="F59">
+        <v>14</v>
+      </c>
+      <c r="G59">
+        <v>1</v>
+      </c>
+      <c r="H59">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="60" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A60" t="s">
+        <v>79</v>
+      </c>
+      <c r="B60" t="s">
+        <v>6</v>
+      </c>
+      <c r="C60" t="s">
+        <v>3</v>
+      </c>
+      <c r="D60" t="s">
+        <v>17</v>
+      </c>
+      <c r="E60" t="s">
+        <v>16</v>
+      </c>
+      <c r="F60">
+        <v>14</v>
+      </c>
+      <c r="G60">
+        <v>1</v>
+      </c>
+      <c r="H60">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A61" t="s">
+        <v>80</v>
+      </c>
+      <c r="B61" t="s">
+        <v>7</v>
+      </c>
+      <c r="C61" t="s">
+        <v>3</v>
+      </c>
+      <c r="D61" t="s">
+        <v>17</v>
+      </c>
+      <c r="E61" t="s">
+        <v>16</v>
+      </c>
+      <c r="F61">
+        <v>14</v>
+      </c>
+      <c r="G61">
+        <v>1</v>
+      </c>
+      <c r="H61">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="62" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A62" t="s">
+        <v>81</v>
+      </c>
+      <c r="B62" t="s">
+        <v>5</v>
+      </c>
+      <c r="C62" t="s">
+        <v>3</v>
+      </c>
+      <c r="D62" t="s">
+        <v>17</v>
+      </c>
+      <c r="E62" t="s">
+        <v>14</v>
+      </c>
+      <c r="F62">
+        <v>14</v>
+      </c>
+      <c r="G62">
+        <v>0.2</v>
+      </c>
+      <c r="H62">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="63" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A63" t="s">
+        <v>82</v>
+      </c>
+      <c r="B63" t="s">
+        <v>6</v>
+      </c>
+      <c r="C63" t="s">
+        <v>3</v>
+      </c>
+      <c r="D63" t="s">
+        <v>17</v>
+      </c>
+      <c r="E63" t="s">
+        <v>14</v>
+      </c>
+      <c r="F63">
+        <v>14</v>
+      </c>
+      <c r="G63">
+        <v>0.2</v>
+      </c>
+      <c r="H63">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="64" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A64" t="s">
+        <v>83</v>
+      </c>
+      <c r="B64" t="s">
+        <v>7</v>
+      </c>
+      <c r="C64" t="s">
+        <v>3</v>
+      </c>
+      <c r="D64" t="s">
+        <v>17</v>
+      </c>
+      <c r="E64" t="s">
+        <v>14</v>
+      </c>
+      <c r="F64">
+        <v>14</v>
+      </c>
+      <c r="G64">
+        <v>0.2</v>
+      </c>
+      <c r="H64">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A65" t="s">
+        <v>84</v>
+      </c>
+      <c r="B65" t="s">
+        <v>5</v>
+      </c>
+      <c r="C65" t="s">
+        <v>12</v>
+      </c>
+      <c r="D65" t="s">
+        <v>4</v>
+      </c>
+      <c r="E65" t="s">
+        <v>15</v>
+      </c>
+      <c r="F65">
+        <v>14</v>
+      </c>
+      <c r="G65">
+        <v>1</v>
+      </c>
+      <c r="H65">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A66" t="s">
+        <v>85</v>
+      </c>
+      <c r="B66" t="s">
+        <v>6</v>
+      </c>
+      <c r="C66" t="s">
+        <v>12</v>
+      </c>
+      <c r="D66" t="s">
+        <v>4</v>
+      </c>
+      <c r="E66" t="s">
+        <v>15</v>
+      </c>
+      <c r="F66">
+        <v>14</v>
+      </c>
+      <c r="G66">
+        <v>1</v>
+      </c>
+      <c r="H66">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A67" t="s">
+        <v>86</v>
+      </c>
+      <c r="B67" t="s">
+        <v>7</v>
+      </c>
+      <c r="C67" t="s">
+        <v>12</v>
+      </c>
+      <c r="D67" t="s">
+        <v>4</v>
+      </c>
+      <c r="E67" t="s">
+        <v>15</v>
+      </c>
+      <c r="F67">
+        <v>14</v>
+      </c>
+      <c r="G67">
+        <v>1</v>
+      </c>
+      <c r="H67">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A68" t="s">
+        <v>87</v>
+      </c>
+      <c r="B68" t="s">
+        <v>5</v>
+      </c>
+      <c r="C68" t="s">
+        <v>12</v>
+      </c>
+      <c r="D68" t="s">
+        <v>17</v>
+      </c>
+      <c r="E68" t="s">
+        <v>16</v>
+      </c>
+      <c r="F68">
+        <v>14</v>
+      </c>
+      <c r="G68">
+        <v>1</v>
+      </c>
+      <c r="H68">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A69" t="s">
+        <v>88</v>
+      </c>
+      <c r="B69" t="s">
+        <v>6</v>
+      </c>
+      <c r="C69" t="s">
+        <v>12</v>
+      </c>
+      <c r="D69" t="s">
+        <v>17</v>
+      </c>
+      <c r="E69" t="s">
+        <v>16</v>
+      </c>
+      <c r="F69">
+        <v>14</v>
+      </c>
+      <c r="G69">
+        <v>1</v>
+      </c>
+      <c r="H69">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A70" t="s">
+        <v>89</v>
+      </c>
+      <c r="B70" t="s">
+        <v>7</v>
+      </c>
+      <c r="C70" t="s">
+        <v>12</v>
+      </c>
+      <c r="D70" t="s">
+        <v>17</v>
+      </c>
+      <c r="E70" t="s">
+        <v>16</v>
+      </c>
+      <c r="F70">
+        <v>14</v>
+      </c>
+      <c r="G70">
+        <v>1</v>
+      </c>
+      <c r="H70">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A71" t="s">
+        <v>90</v>
+      </c>
+      <c r="B71" t="s">
+        <v>5</v>
+      </c>
+      <c r="C71" t="s">
+        <v>12</v>
+      </c>
+      <c r="D71" t="s">
+        <v>17</v>
+      </c>
+      <c r="E71" t="s">
+        <v>14</v>
+      </c>
+      <c r="F71">
+        <v>14</v>
+      </c>
+      <c r="G71">
+        <v>0.2</v>
+      </c>
+      <c r="H71">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A72" t="s">
+        <v>91</v>
+      </c>
+      <c r="B72" t="s">
+        <v>6</v>
+      </c>
+      <c r="C72" t="s">
+        <v>12</v>
+      </c>
+      <c r="D72" t="s">
+        <v>17</v>
+      </c>
+      <c r="E72" t="s">
+        <v>14</v>
+      </c>
+      <c r="F72">
+        <v>14</v>
+      </c>
+      <c r="G72">
+        <v>0.2</v>
+      </c>
+      <c r="H72">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A73" t="s">
+        <v>92</v>
+      </c>
+      <c r="B73" t="s">
+        <v>7</v>
+      </c>
+      <c r="C73" t="s">
+        <v>12</v>
+      </c>
+      <c r="D73" t="s">
+        <v>17</v>
+      </c>
+      <c r="E73" t="s">
+        <v>14</v>
+      </c>
+      <c r="F73">
+        <v>14</v>
+      </c>
+      <c r="G73">
+        <v>0.2</v>
+      </c>
+      <c r="H73">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A74" t="s">
+        <v>93</v>
+      </c>
+      <c r="B74" t="s">
+        <v>5</v>
+      </c>
+      <c r="C74" t="s">
+        <v>13</v>
+      </c>
+      <c r="D74" t="s">
+        <v>4</v>
+      </c>
+      <c r="E74" t="s">
+        <v>15</v>
+      </c>
+      <c r="F74">
+        <v>14</v>
+      </c>
+      <c r="G74">
+        <v>1</v>
+      </c>
+      <c r="H74">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A75" t="s">
+        <v>94</v>
+      </c>
+      <c r="B75" t="s">
+        <v>6</v>
+      </c>
+      <c r="C75" t="s">
+        <v>13</v>
+      </c>
+      <c r="D75" t="s">
+        <v>4</v>
+      </c>
+      <c r="E75" t="s">
+        <v>15</v>
+      </c>
+      <c r="F75">
+        <v>14</v>
+      </c>
+      <c r="G75">
+        <v>1</v>
+      </c>
+      <c r="H75">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A76" t="s">
+        <v>95</v>
+      </c>
+      <c r="B76" t="s">
+        <v>7</v>
+      </c>
+      <c r="C76" t="s">
+        <v>13</v>
+      </c>
+      <c r="D76" t="s">
+        <v>4</v>
+      </c>
+      <c r="E76" t="s">
+        <v>15</v>
+      </c>
+      <c r="F76">
+        <v>14</v>
+      </c>
+      <c r="G76">
+        <v>1</v>
+      </c>
+      <c r="H76">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A77" t="s">
+        <v>96</v>
+      </c>
+      <c r="B77" t="s">
+        <v>5</v>
+      </c>
+      <c r="C77" t="s">
+        <v>13</v>
+      </c>
+      <c r="D77" t="s">
+        <v>17</v>
+      </c>
+      <c r="E77" t="s">
+        <v>16</v>
+      </c>
+      <c r="F77">
+        <v>14</v>
+      </c>
+      <c r="G77">
+        <v>1</v>
+      </c>
+      <c r="H77">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A78" t="s">
+        <v>97</v>
+      </c>
+      <c r="B78" t="s">
+        <v>6</v>
+      </c>
+      <c r="C78" t="s">
+        <v>13</v>
+      </c>
+      <c r="D78" t="s">
+        <v>17</v>
+      </c>
+      <c r="E78" t="s">
+        <v>16</v>
+      </c>
+      <c r="F78">
+        <v>14</v>
+      </c>
+      <c r="G78">
+        <v>1</v>
+      </c>
+      <c r="H78">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A79" t="s">
+        <v>98</v>
+      </c>
+      <c r="B79" t="s">
+        <v>7</v>
+      </c>
+      <c r="C79" t="s">
+        <v>13</v>
+      </c>
+      <c r="D79" t="s">
+        <v>17</v>
+      </c>
+      <c r="E79" t="s">
+        <v>16</v>
+      </c>
+      <c r="F79">
+        <v>14</v>
+      </c>
+      <c r="G79">
+        <v>1</v>
+      </c>
+      <c r="H79">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A80" t="s">
+        <v>99</v>
+      </c>
+      <c r="B80" t="s">
+        <v>5</v>
+      </c>
+      <c r="C80" t="s">
+        <v>13</v>
+      </c>
+      <c r="D80" t="s">
+        <v>17</v>
+      </c>
+      <c r="E80" t="s">
+        <v>14</v>
+      </c>
+      <c r="F80">
+        <v>14</v>
+      </c>
+      <c r="G80">
+        <v>0.2</v>
+      </c>
+      <c r="H80">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A81" t="s">
+        <v>100</v>
+      </c>
+      <c r="B81" t="s">
+        <v>6</v>
+      </c>
+      <c r="C81" t="s">
+        <v>13</v>
+      </c>
+      <c r="D81" t="s">
+        <v>17</v>
+      </c>
+      <c r="E81" t="s">
+        <v>14</v>
+      </c>
+      <c r="F81">
+        <v>14</v>
+      </c>
+      <c r="G81">
+        <v>0.2</v>
+      </c>
+      <c r="H81">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A82" t="s">
+        <v>101</v>
+      </c>
+      <c r="B82" t="s">
+        <v>7</v>
+      </c>
+      <c r="C82" t="s">
+        <v>13</v>
+      </c>
+      <c r="D82" t="s">
+        <v>17</v>
+      </c>
+      <c r="E82" t="s">
+        <v>14</v>
+      </c>
+      <c r="F82">
+        <v>14</v>
+      </c>
+      <c r="G82">
+        <v>0.2</v>
+      </c>
+      <c r="H82">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A83" t="s">
+        <v>102</v>
+      </c>
+      <c r="B83" t="s">
+        <v>5</v>
+      </c>
+      <c r="C83" t="s">
+        <v>3</v>
+      </c>
+      <c r="D83" t="s">
+        <v>4</v>
+      </c>
+      <c r="E83" t="s">
+        <v>15</v>
+      </c>
+      <c r="F83">
+        <v>21</v>
+      </c>
+      <c r="G83">
+        <v>1</v>
+      </c>
+      <c r="H83">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A84" t="s">
+        <v>103</v>
+      </c>
+      <c r="B84" t="s">
+        <v>6</v>
+      </c>
+      <c r="C84" t="s">
+        <v>3</v>
+      </c>
+      <c r="D84" t="s">
+        <v>4</v>
+      </c>
+      <c r="E84" t="s">
+        <v>15</v>
+      </c>
+      <c r="F84">
+        <v>21</v>
+      </c>
+      <c r="G84">
+        <v>1</v>
+      </c>
+      <c r="H84">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A85" t="s">
+        <v>104</v>
+      </c>
+      <c r="B85" t="s">
+        <v>7</v>
+      </c>
+      <c r="C85" t="s">
+        <v>3</v>
+      </c>
+      <c r="D85" t="s">
+        <v>4</v>
+      </c>
+      <c r="E85" t="s">
+        <v>15</v>
+      </c>
+      <c r="F85">
+        <v>21</v>
+      </c>
+      <c r="G85">
+        <v>1</v>
+      </c>
+      <c r="H85">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A86" t="s">
+        <v>105</v>
+      </c>
+      <c r="B86" t="s">
+        <v>5</v>
+      </c>
+      <c r="C86" t="s">
+        <v>3</v>
+      </c>
+      <c r="D86" t="s">
+        <v>17</v>
+      </c>
+      <c r="E86" t="s">
+        <v>16</v>
+      </c>
+      <c r="F86">
+        <v>21</v>
+      </c>
+      <c r="G86">
+        <v>1</v>
+      </c>
+      <c r="H86">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A87" t="s">
+        <v>106</v>
+      </c>
+      <c r="B87" t="s">
+        <v>6</v>
+      </c>
+      <c r="C87" t="s">
+        <v>3</v>
+      </c>
+      <c r="D87" t="s">
+        <v>17</v>
+      </c>
+      <c r="E87" t="s">
+        <v>16</v>
+      </c>
+      <c r="F87">
+        <v>21</v>
+      </c>
+      <c r="G87">
+        <v>1</v>
+      </c>
+      <c r="H87">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A88" t="s">
+        <v>107</v>
+      </c>
+      <c r="B88" t="s">
+        <v>7</v>
+      </c>
+      <c r="C88" t="s">
+        <v>3</v>
+      </c>
+      <c r="D88" t="s">
+        <v>17</v>
+      </c>
+      <c r="E88" t="s">
+        <v>16</v>
+      </c>
+      <c r="F88">
+        <v>21</v>
+      </c>
+      <c r="G88">
+        <v>1</v>
+      </c>
+      <c r="H88">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A89" t="s">
+        <v>108</v>
+      </c>
+      <c r="B89" t="s">
+        <v>5</v>
+      </c>
+      <c r="C89" t="s">
+        <v>3</v>
+      </c>
+      <c r="D89" t="s">
+        <v>17</v>
+      </c>
+      <c r="E89" t="s">
+        <v>14</v>
+      </c>
+      <c r="F89">
+        <v>21</v>
+      </c>
+      <c r="G89">
+        <v>0.2</v>
+      </c>
+      <c r="H89">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="90" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A90" t="s">
+        <v>109</v>
+      </c>
+      <c r="B90" t="s">
+        <v>6</v>
+      </c>
+      <c r="C90" t="s">
+        <v>3</v>
+      </c>
+      <c r="D90" t="s">
+        <v>17</v>
+      </c>
+      <c r="E90" t="s">
+        <v>14</v>
+      </c>
+      <c r="F90">
+        <v>21</v>
+      </c>
+      <c r="G90">
+        <v>0.2</v>
+      </c>
+      <c r="H90">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A91" t="s">
+        <v>110</v>
+      </c>
+      <c r="B91" t="s">
+        <v>7</v>
+      </c>
+      <c r="C91" t="s">
+        <v>3</v>
+      </c>
+      <c r="D91" t="s">
+        <v>17</v>
+      </c>
+      <c r="E91" t="s">
+        <v>14</v>
+      </c>
+      <c r="F91">
+        <v>21</v>
+      </c>
+      <c r="G91">
+        <v>0.2</v>
+      </c>
+      <c r="H91">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="92" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A92" t="s">
+        <v>111</v>
+      </c>
+      <c r="B92" t="s">
+        <v>5</v>
+      </c>
+      <c r="C92" t="s">
+        <v>12</v>
+      </c>
+      <c r="D92" t="s">
+        <v>4</v>
+      </c>
+      <c r="E92" t="s">
+        <v>15</v>
+      </c>
+      <c r="F92">
+        <v>21</v>
+      </c>
+      <c r="G92">
+        <v>1</v>
+      </c>
+      <c r="H92">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="93" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A93" t="s">
+        <v>112</v>
+      </c>
+      <c r="B93" t="s">
+        <v>6</v>
+      </c>
+      <c r="C93" t="s">
+        <v>12</v>
+      </c>
+      <c r="D93" t="s">
+        <v>4</v>
+      </c>
+      <c r="E93" t="s">
+        <v>15</v>
+      </c>
+      <c r="F93">
+        <v>21</v>
+      </c>
+      <c r="G93">
+        <v>1</v>
+      </c>
+      <c r="H93">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="94" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A94" t="s">
+        <v>113</v>
+      </c>
+      <c r="B94" t="s">
+        <v>7</v>
+      </c>
+      <c r="C94" t="s">
+        <v>12</v>
+      </c>
+      <c r="D94" t="s">
+        <v>4</v>
+      </c>
+      <c r="E94" t="s">
+        <v>15</v>
+      </c>
+      <c r="F94">
+        <v>21</v>
+      </c>
+      <c r="G94">
+        <v>1</v>
+      </c>
+      <c r="H94">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="95" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A95" t="s">
+        <v>114</v>
+      </c>
+      <c r="B95" t="s">
+        <v>5</v>
+      </c>
+      <c r="C95" t="s">
+        <v>12</v>
+      </c>
+      <c r="D95" t="s">
+        <v>17</v>
+      </c>
+      <c r="E95" t="s">
+        <v>16</v>
+      </c>
+      <c r="F95">
+        <v>21</v>
+      </c>
+      <c r="G95">
+        <v>1</v>
+      </c>
+      <c r="H95">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="96" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A96" t="s">
+        <v>115</v>
+      </c>
+      <c r="B96" t="s">
+        <v>6</v>
+      </c>
+      <c r="C96" t="s">
+        <v>12</v>
+      </c>
+      <c r="D96" t="s">
+        <v>17</v>
+      </c>
+      <c r="E96" t="s">
+        <v>16</v>
+      </c>
+      <c r="F96">
+        <v>21</v>
+      </c>
+      <c r="G96">
+        <v>1</v>
+      </c>
+      <c r="H96">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="97" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A97" t="s">
+        <v>116</v>
+      </c>
+      <c r="B97" t="s">
+        <v>7</v>
+      </c>
+      <c r="C97" t="s">
+        <v>12</v>
+      </c>
+      <c r="D97" t="s">
+        <v>17</v>
+      </c>
+      <c r="E97" t="s">
+        <v>16</v>
+      </c>
+      <c r="F97">
+        <v>21</v>
+      </c>
+      <c r="G97">
+        <v>1</v>
+      </c>
+      <c r="H97">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="98" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A98" t="s">
+        <v>117</v>
+      </c>
+      <c r="B98" t="s">
+        <v>5</v>
+      </c>
+      <c r="C98" t="s">
+        <v>12</v>
+      </c>
+      <c r="D98" t="s">
+        <v>17</v>
+      </c>
+      <c r="E98" t="s">
+        <v>14</v>
+      </c>
+      <c r="F98">
+        <v>21</v>
+      </c>
+      <c r="G98">
+        <v>0.2</v>
+      </c>
+      <c r="H98">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="99" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A99" t="s">
+        <v>118</v>
+      </c>
+      <c r="B99" t="s">
+        <v>6</v>
+      </c>
+      <c r="C99" t="s">
+        <v>12</v>
+      </c>
+      <c r="D99" t="s">
+        <v>17</v>
+      </c>
+      <c r="E99" t="s">
+        <v>14</v>
+      </c>
+      <c r="F99">
+        <v>21</v>
+      </c>
+      <c r="G99">
+        <v>0.2</v>
+      </c>
+      <c r="H99">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="100" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A100" t="s">
+        <v>119</v>
+      </c>
+      <c r="B100" t="s">
+        <v>7</v>
+      </c>
+      <c r="C100" t="s">
+        <v>12</v>
+      </c>
+      <c r="D100" t="s">
+        <v>17</v>
+      </c>
+      <c r="E100" t="s">
+        <v>14</v>
+      </c>
+      <c r="F100">
+        <v>21</v>
+      </c>
+      <c r="G100">
+        <v>0.2</v>
+      </c>
+      <c r="H100">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="101" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A101" t="s">
+        <v>120</v>
+      </c>
+      <c r="B101" t="s">
+        <v>5</v>
+      </c>
+      <c r="C101" t="s">
+        <v>13</v>
+      </c>
+      <c r="D101" t="s">
+        <v>4</v>
+      </c>
+      <c r="E101" t="s">
+        <v>15</v>
+      </c>
+      <c r="F101">
+        <v>21</v>
+      </c>
+      <c r="G101">
+        <v>1</v>
+      </c>
+      <c r="H101">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="102" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A102" t="s">
+        <v>121</v>
+      </c>
+      <c r="B102" t="s">
+        <v>6</v>
+      </c>
+      <c r="C102" t="s">
+        <v>13</v>
+      </c>
+      <c r="D102" t="s">
+        <v>4</v>
+      </c>
+      <c r="E102" t="s">
+        <v>15</v>
+      </c>
+      <c r="F102">
+        <v>21</v>
+      </c>
+      <c r="G102">
+        <v>1</v>
+      </c>
+      <c r="H102">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="103" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A103" t="s">
+        <v>122</v>
+      </c>
+      <c r="B103" t="s">
+        <v>7</v>
+      </c>
+      <c r="C103" t="s">
+        <v>13</v>
+      </c>
+      <c r="D103" t="s">
+        <v>4</v>
+      </c>
+      <c r="E103" t="s">
+        <v>15</v>
+      </c>
+      <c r="F103">
+        <v>21</v>
+      </c>
+      <c r="G103">
+        <v>1</v>
+      </c>
+      <c r="H103">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="104" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A104" t="s">
+        <v>123</v>
+      </c>
+      <c r="B104" t="s">
+        <v>5</v>
+      </c>
+      <c r="C104" t="s">
+        <v>13</v>
+      </c>
+      <c r="D104" t="s">
+        <v>17</v>
+      </c>
+      <c r="E104" t="s">
+        <v>16</v>
+      </c>
+      <c r="F104">
+        <v>21</v>
+      </c>
+      <c r="G104">
+        <v>1</v>
+      </c>
+      <c r="H104">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="105" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A105" t="s">
+        <v>124</v>
+      </c>
+      <c r="B105" t="s">
+        <v>6</v>
+      </c>
+      <c r="C105" t="s">
+        <v>13</v>
+      </c>
+      <c r="D105" t="s">
+        <v>17</v>
+      </c>
+      <c r="E105" t="s">
+        <v>16</v>
+      </c>
+      <c r="F105">
+        <v>21</v>
+      </c>
+      <c r="G105">
+        <v>1</v>
+      </c>
+      <c r="H105">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="106" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A106" t="s">
+        <v>125</v>
+      </c>
+      <c r="B106" t="s">
+        <v>7</v>
+      </c>
+      <c r="C106" t="s">
+        <v>13</v>
+      </c>
+      <c r="D106" t="s">
+        <v>17</v>
+      </c>
+      <c r="E106" t="s">
+        <v>16</v>
+      </c>
+      <c r="F106">
+        <v>21</v>
+      </c>
+      <c r="G106">
+        <v>1</v>
+      </c>
+      <c r="H106">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="107" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A107" t="s">
+        <v>126</v>
+      </c>
+      <c r="B107" t="s">
+        <v>5</v>
+      </c>
+      <c r="C107" t="s">
+        <v>13</v>
+      </c>
+      <c r="D107" t="s">
+        <v>17</v>
+      </c>
+      <c r="E107" t="s">
+        <v>14</v>
+      </c>
+      <c r="F107">
+        <v>21</v>
+      </c>
+      <c r="G107">
+        <v>0.2</v>
+      </c>
+      <c r="H107">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="108" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A108" t="s">
+        <v>127</v>
+      </c>
+      <c r="B108" t="s">
+        <v>6</v>
+      </c>
+      <c r="C108" t="s">
+        <v>13</v>
+      </c>
+      <c r="D108" t="s">
+        <v>17</v>
+      </c>
+      <c r="E108" t="s">
+        <v>14</v>
+      </c>
+      <c r="F108">
+        <v>21</v>
+      </c>
+      <c r="G108">
+        <v>0.2</v>
+      </c>
+      <c r="H108">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="109" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A109" t="s">
+        <v>128</v>
+      </c>
+      <c r="B109" t="s">
+        <v>7</v>
+      </c>
+      <c r="C109" t="s">
+        <v>13</v>
+      </c>
+      <c r="D109" t="s">
+        <v>17</v>
+      </c>
+      <c r="E109" t="s">
+        <v>14</v>
+      </c>
+      <c r="F109">
+        <v>21</v>
+      </c>
+      <c r="G109">
+        <v>0.2</v>
+      </c>
+      <c r="H109">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="110" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A110" t="s">
+        <v>129</v>
+      </c>
+      <c r="B110" t="s">
+        <v>5</v>
+      </c>
+      <c r="C110" t="s">
+        <v>3</v>
+      </c>
+      <c r="D110" t="s">
+        <v>4</v>
+      </c>
+      <c r="E110" t="s">
+        <v>15</v>
+      </c>
+      <c r="F110">
+        <v>42</v>
+      </c>
+      <c r="G110">
+        <v>1</v>
+      </c>
+      <c r="H110">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="111" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A111" t="s">
+        <v>130</v>
+      </c>
+      <c r="B111" t="s">
+        <v>6</v>
+      </c>
+      <c r="C111" t="s">
+        <v>3</v>
+      </c>
+      <c r="D111" t="s">
+        <v>4</v>
+      </c>
+      <c r="E111" t="s">
+        <v>15</v>
+      </c>
+      <c r="F111">
+        <v>42</v>
+      </c>
+      <c r="G111">
+        <v>1</v>
+      </c>
+      <c r="H111">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="112" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A112" t="s">
+        <v>131</v>
+      </c>
+      <c r="B112" t="s">
+        <v>7</v>
+      </c>
+      <c r="C112" t="s">
+        <v>3</v>
+      </c>
+      <c r="D112" t="s">
+        <v>4</v>
+      </c>
+      <c r="E112" t="s">
+        <v>15</v>
+      </c>
+      <c r="F112">
+        <v>42</v>
+      </c>
+      <c r="G112">
+        <v>1</v>
+      </c>
+      <c r="H112">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="113" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A113" t="s">
+        <v>132</v>
+      </c>
+      <c r="B113" t="s">
+        <v>5</v>
+      </c>
+      <c r="C113" t="s">
+        <v>3</v>
+      </c>
+      <c r="D113" t="s">
+        <v>17</v>
+      </c>
+      <c r="E113" t="s">
+        <v>16</v>
+      </c>
+      <c r="F113">
+        <v>42</v>
+      </c>
+      <c r="G113">
+        <v>1</v>
+      </c>
+      <c r="H113">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="114" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A114" t="s">
+        <v>133</v>
+      </c>
+      <c r="B114" t="s">
+        <v>6</v>
+      </c>
+      <c r="C114" t="s">
+        <v>3</v>
+      </c>
+      <c r="D114" t="s">
+        <v>17</v>
+      </c>
+      <c r="E114" t="s">
+        <v>16</v>
+      </c>
+      <c r="F114">
+        <v>42</v>
+      </c>
+      <c r="G114">
+        <v>1</v>
+      </c>
+      <c r="H114">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="115" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A115" t="s">
+        <v>134</v>
+      </c>
+      <c r="B115" t="s">
+        <v>7</v>
+      </c>
+      <c r="C115" t="s">
+        <v>3</v>
+      </c>
+      <c r="D115" t="s">
+        <v>17</v>
+      </c>
+      <c r="E115" t="s">
+        <v>16</v>
+      </c>
+      <c r="F115">
+        <v>42</v>
+      </c>
+      <c r="G115">
+        <v>1</v>
+      </c>
+      <c r="H115">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="116" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A116" t="s">
+        <v>135</v>
+      </c>
+      <c r="B116" t="s">
+        <v>5</v>
+      </c>
+      <c r="C116" t="s">
+        <v>3</v>
+      </c>
+      <c r="D116" t="s">
+        <v>17</v>
+      </c>
+      <c r="E116" t="s">
+        <v>14</v>
+      </c>
+      <c r="F116">
+        <v>42</v>
+      </c>
+      <c r="G116">
+        <v>0.2</v>
+      </c>
+      <c r="H116">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="117" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A117" t="s">
+        <v>136</v>
+      </c>
+      <c r="B117" t="s">
+        <v>6</v>
+      </c>
+      <c r="C117" t="s">
+        <v>3</v>
+      </c>
+      <c r="D117" t="s">
+        <v>17</v>
+      </c>
+      <c r="E117" t="s">
+        <v>14</v>
+      </c>
+      <c r="F117">
+        <v>42</v>
+      </c>
+      <c r="G117">
+        <v>0.2</v>
+      </c>
+      <c r="H117">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="118" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A118" t="s">
+        <v>137</v>
+      </c>
+      <c r="B118" t="s">
+        <v>7</v>
+      </c>
+      <c r="C118" t="s">
+        <v>3</v>
+      </c>
+      <c r="D118" t="s">
+        <v>17</v>
+      </c>
+      <c r="E118" t="s">
+        <v>14</v>
+      </c>
+      <c r="F118">
+        <v>42</v>
+      </c>
+      <c r="G118">
+        <v>0.2</v>
+      </c>
+      <c r="H118">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="119" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A119" t="s">
+        <v>138</v>
+      </c>
+      <c r="B119" t="s">
+        <v>5</v>
+      </c>
+      <c r="C119" t="s">
+        <v>12</v>
+      </c>
+      <c r="D119" t="s">
+        <v>4</v>
+      </c>
+      <c r="E119" t="s">
+        <v>15</v>
+      </c>
+      <c r="F119">
+        <v>42</v>
+      </c>
+      <c r="G119">
+        <v>1</v>
+      </c>
+      <c r="H119">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="120" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A120" t="s">
+        <v>139</v>
+      </c>
+      <c r="B120" t="s">
+        <v>6</v>
+      </c>
+      <c r="C120" t="s">
+        <v>12</v>
+      </c>
+      <c r="D120" t="s">
+        <v>4</v>
+      </c>
+      <c r="E120" t="s">
+        <v>15</v>
+      </c>
+      <c r="F120">
+        <v>42</v>
+      </c>
+      <c r="G120">
+        <v>1</v>
+      </c>
+      <c r="H120">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="121" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A121" t="s">
+        <v>140</v>
+      </c>
+      <c r="B121" t="s">
+        <v>7</v>
+      </c>
+      <c r="C121" t="s">
+        <v>12</v>
+      </c>
+      <c r="D121" t="s">
+        <v>4</v>
+      </c>
+      <c r="E121" t="s">
+        <v>15</v>
+      </c>
+      <c r="F121">
+        <v>42</v>
+      </c>
+      <c r="G121">
+        <v>1</v>
+      </c>
+      <c r="H121">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="122" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A122" t="s">
+        <v>141</v>
+      </c>
+      <c r="B122" t="s">
+        <v>5</v>
+      </c>
+      <c r="C122" t="s">
+        <v>12</v>
+      </c>
+      <c r="D122" t="s">
+        <v>17</v>
+      </c>
+      <c r="E122" t="s">
+        <v>16</v>
+      </c>
+      <c r="F122">
+        <v>42</v>
+      </c>
+      <c r="G122">
+        <v>1</v>
+      </c>
+      <c r="H122">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="123" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A123" t="s">
+        <v>142</v>
+      </c>
+      <c r="B123" t="s">
+        <v>6</v>
+      </c>
+      <c r="C123" t="s">
+        <v>12</v>
+      </c>
+      <c r="D123" t="s">
+        <v>17</v>
+      </c>
+      <c r="E123" t="s">
+        <v>16</v>
+      </c>
+      <c r="F123">
+        <v>42</v>
+      </c>
+      <c r="G123">
+        <v>1</v>
+      </c>
+      <c r="H123">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="124" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A124" t="s">
+        <v>143</v>
+      </c>
+      <c r="B124" t="s">
+        <v>7</v>
+      </c>
+      <c r="C124" t="s">
+        <v>12</v>
+      </c>
+      <c r="D124" t="s">
+        <v>17</v>
+      </c>
+      <c r="E124" t="s">
+        <v>16</v>
+      </c>
+      <c r="F124">
+        <v>42</v>
+      </c>
+      <c r="G124">
+        <v>1</v>
+      </c>
+      <c r="H124">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="125" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A125" t="s">
+        <v>144</v>
+      </c>
+      <c r="B125" t="s">
+        <v>5</v>
+      </c>
+      <c r="C125" t="s">
+        <v>12</v>
+      </c>
+      <c r="D125" t="s">
+        <v>17</v>
+      </c>
+      <c r="E125" t="s">
+        <v>14</v>
+      </c>
+      <c r="F125">
+        <v>42</v>
+      </c>
+      <c r="G125">
+        <v>0.2</v>
+      </c>
+      <c r="H125">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="126" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A126" t="s">
+        <v>145</v>
+      </c>
+      <c r="B126" t="s">
+        <v>6</v>
+      </c>
+      <c r="C126" t="s">
+        <v>12</v>
+      </c>
+      <c r="D126" t="s">
+        <v>17</v>
+      </c>
+      <c r="E126" t="s">
+        <v>14</v>
+      </c>
+      <c r="F126">
+        <v>42</v>
+      </c>
+      <c r="G126">
+        <v>0.2</v>
+      </c>
+      <c r="H126">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="127" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A127" t="s">
+        <v>146</v>
+      </c>
+      <c r="B127" t="s">
+        <v>7</v>
+      </c>
+      <c r="C127" t="s">
+        <v>12</v>
+      </c>
+      <c r="D127" t="s">
+        <v>17</v>
+      </c>
+      <c r="E127" t="s">
+        <v>14</v>
+      </c>
+      <c r="F127">
+        <v>42</v>
+      </c>
+      <c r="G127">
+        <v>0.2</v>
+      </c>
+      <c r="H127">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="128" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A128" t="s">
+        <v>147</v>
+      </c>
+      <c r="B128" t="s">
+        <v>5</v>
+      </c>
+      <c r="C128" t="s">
+        <v>13</v>
+      </c>
+      <c r="D128" t="s">
+        <v>4</v>
+      </c>
+      <c r="E128" t="s">
+        <v>15</v>
+      </c>
+      <c r="F128">
+        <v>42</v>
+      </c>
+      <c r="G128">
+        <v>1</v>
+      </c>
+      <c r="H128">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="129" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A129" t="s">
+        <v>148</v>
+      </c>
+      <c r="B129" t="s">
+        <v>6</v>
+      </c>
+      <c r="C129" t="s">
+        <v>13</v>
+      </c>
+      <c r="D129" t="s">
+        <v>4</v>
+      </c>
+      <c r="E129" t="s">
+        <v>15</v>
+      </c>
+      <c r="F129">
+        <v>42</v>
+      </c>
+      <c r="G129">
+        <v>1</v>
+      </c>
+      <c r="H129">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="130" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A130" t="s">
+        <v>149</v>
+      </c>
+      <c r="B130" t="s">
+        <v>7</v>
+      </c>
+      <c r="C130" t="s">
+        <v>13</v>
+      </c>
+      <c r="D130" t="s">
+        <v>4</v>
+      </c>
+      <c r="E130" t="s">
+        <v>15</v>
+      </c>
+      <c r="F130">
+        <v>42</v>
+      </c>
+      <c r="G130">
+        <v>1</v>
+      </c>
+      <c r="H130">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="131" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A131" t="s">
+        <v>150</v>
+      </c>
+      <c r="B131" t="s">
+        <v>5</v>
+      </c>
+      <c r="C131" t="s">
+        <v>13</v>
+      </c>
+      <c r="D131" t="s">
+        <v>17</v>
+      </c>
+      <c r="E131" t="s">
+        <v>16</v>
+      </c>
+      <c r="F131">
+        <v>42</v>
+      </c>
+      <c r="G131">
+        <v>1</v>
+      </c>
+      <c r="H131">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="132" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A132" t="s">
+        <v>151</v>
+      </c>
+      <c r="B132" t="s">
+        <v>6</v>
+      </c>
+      <c r="C132" t="s">
+        <v>13</v>
+      </c>
+      <c r="D132" t="s">
+        <v>17</v>
+      </c>
+      <c r="E132" t="s">
+        <v>16</v>
+      </c>
+      <c r="F132">
+        <v>42</v>
+      </c>
+      <c r="G132">
+        <v>1</v>
+      </c>
+      <c r="H132">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="133" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A133" t="s">
+        <v>152</v>
+      </c>
+      <c r="B133" t="s">
+        <v>7</v>
+      </c>
+      <c r="C133" t="s">
+        <v>13</v>
+      </c>
+      <c r="D133" t="s">
+        <v>17</v>
+      </c>
+      <c r="E133" t="s">
+        <v>16</v>
+      </c>
+      <c r="F133">
+        <v>42</v>
+      </c>
+      <c r="G133">
+        <v>1</v>
+      </c>
+      <c r="H133">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="134" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A134" t="s">
+        <v>153</v>
+      </c>
+      <c r="B134" t="s">
+        <v>5</v>
+      </c>
+      <c r="C134" t="s">
+        <v>13</v>
+      </c>
+      <c r="D134" t="s">
+        <v>17</v>
+      </c>
+      <c r="E134" t="s">
+        <v>14</v>
+      </c>
+      <c r="F134">
+        <v>42</v>
+      </c>
+      <c r="G134">
+        <v>0.2</v>
+      </c>
+      <c r="H134">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="135" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A135" t="s">
+        <v>154</v>
+      </c>
+      <c r="B135" t="s">
+        <v>6</v>
+      </c>
+      <c r="C135" t="s">
+        <v>13</v>
+      </c>
+      <c r="D135" t="s">
+        <v>17</v>
+      </c>
+      <c r="E135" t="s">
+        <v>14</v>
+      </c>
+      <c r="F135">
+        <v>42</v>
+      </c>
+      <c r="G135">
+        <v>0.2</v>
+      </c>
+      <c r="H135">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="136" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A136" t="s">
+        <v>155</v>
+      </c>
+      <c r="B136" t="s">
+        <v>7</v>
+      </c>
+      <c r="C136" t="s">
+        <v>13</v>
+      </c>
+      <c r="D136" t="s">
+        <v>17</v>
+      </c>
+      <c r="E136" t="s">
+        <v>14</v>
+      </c>
+      <c r="F136">
+        <v>42</v>
+      </c>
+      <c r="G136">
+        <v>0.2</v>
+      </c>
+      <c r="H136">
+        <v>150</v>
       </c>
     </row>
   </sheetData>
